--- a/Projeto/resultados_todos_comites.xlsx
+++ b/Projeto/resultados_todos_comites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gilcesarf/git/repositories/imd/imd3002-202502/Projeto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AFC89E-1548-5B4B-B1A5-0D4B41D359F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0EEBFC-1628-3443-A4DB-65FA734B6769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-61280" yWindow="4180" windowWidth="54900" windowHeight="25000" activeTab="4" xr2:uid="{DB75B333-2FE5-1348-BF63-C184A4857D39}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="41120" windowHeight="25700" activeTab="4" xr2:uid="{DB75B333-2FE5-1348-BF63-C184A4857D39}"/>
   </bookViews>
   <sheets>
     <sheet name="Bagging" sheetId="2" r:id="rId1"/>
@@ -25,8 +25,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="61" r:id="rId7"/>
-    <pivotCache cacheId="62" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19380,707 +19380,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F72AC3A9-0A87-554A-8C41-91BA0F4E309B}" name="Tabela dinâmica5" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A49:B61" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="28">
-        <item x="16"/>
-        <item x="19"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="24"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="3"/>
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="6"/>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="10"/>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="11"/>
-      <x v="20"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{06409053-846E-BE4E-876F-D16480FD488E}" name="Tabela dinâmica5" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="28">
-        <item x="16"/>
-        <item x="19"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="24"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="3"/>
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="26"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E36D2FA6-3B83-E949-AFEB-9AAE6212B93E}" name="Tabela dinâmica4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="P3:T8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="4">
-    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
-    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96AF3837-ACF6-EA4A-86B5-D2E18F30D621}" name="Tabela dinâmica1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:F29" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="12">
-        <item x="10"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="7"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="28">
-        <item x="16"/>
-        <item x="19"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="24"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="2">
-        <item x="1"/>
-        <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="0"/>
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="25">
-    <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="6"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="10"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="11"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43A66ABC-F701-E349-91FE-0928348E21D5}" name="Tabela dinâmica4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="P3:T16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="4">
-    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
-    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBB1CF52-3D0E-8B4D-832E-467A81C7991F}" name="Tabela dinâmica1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBB1CF52-3D0E-8B4D-832E-467A81C7991F}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N29" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -20319,8 +19619,708 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96AF3837-ACF6-EA4A-86B5-D2E18F30D621}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:F29" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="12">
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="7"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="28">
+        <item x="16"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="24"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{06409053-846E-BE4E-876F-D16480FD488E}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="28">
+        <item x="16"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="24"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="26"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E36D2FA6-3B83-E949-AFEB-9AAE6212B93E}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="P3:T8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="4">
+    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F72AC3A9-0A87-554A-8C41-91BA0F4E309B}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A49:B61" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="28">
+        <item x="16"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="24"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x v="20"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43A66ABC-F701-E349-91FE-0928348E21D5}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="P3:T16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="4">
+    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29F03245-D0A4-9346-ACB5-8FA989F63DE8}" name="Tabela dinâmica5" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29F03245-D0A4-9346-ACB5-8FA989F63DE8}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A49:B61" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -20460,7 +20460,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16F8ED69-12D5-8241-ADF8-D9CA21B77726}" name="Tabela dinâmica1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16F8ED69-12D5-8241-ADF8-D9CA21B77726}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N29" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -20700,7 +20700,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29322624-C5A0-D44E-8E86-46DE173AA181}" name="Tabela dinâmica4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29322624-C5A0-D44E-8E86-46DE173AA181}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="P3:T16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -20830,113 +20830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B74FD9E-820D-E34F-A571-2AC8DE3147FD}" name="Tabela dinâmica4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="P3:T8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="4">
-    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
-    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AEFCDCA-25B7-CF42-92CB-CFF2777D4CEB}" name="Tabela dinâmica5" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AEFCDCA-25B7-CF42-92CB-CFF2777D4CEB}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -21043,8 +20937,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98BB5990-B82A-7742-977A-71599871313C}" name="Tabela dinâmica1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98BB5990-B82A-7742-977A-71599871313C}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F29" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -21254,6 +21148,112 @@
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B74FD9E-820D-E34F-A571-2AC8DE3147FD}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="P3:T8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="4">
+    <dataField name="Média de f1_score" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="DesvPad de f1_score" fld="6" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Média de execution_time" fld="9" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="DesvPad de execution_time" fld="9" subtotal="stdDev" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -27432,7 +27432,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2CAECE-6B20-1E49-B0CD-9C7C866ACF1B}">
-  <dimension ref="B2:O40"/>
+  <dimension ref="B2:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -27532,15 +27532,15 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <f>_xlfn.RANK.EQ(F4,$E4:$H4,1)</f>
+        <f t="shared" ref="K4:K18" si="1">_xlfn.RANK.EQ(F4,$E4:$H4,1)</f>
         <v>4</v>
       </c>
       <c r="L4">
-        <f>_xlfn.RANK.EQ(G4,$E4:$H4,1)</f>
+        <f t="shared" ref="L4:L18" si="2">_xlfn.RANK.EQ(G4,$E4:$H4,1)</f>
         <v>1</v>
       </c>
       <c r="M4">
-        <f>_xlfn.RANK.EQ(H4,$E4:$H4,1)</f>
+        <f t="shared" ref="M4:M18" si="3">_xlfn.RANK.EQ(H4,$E4:$H4,1)</f>
         <v>2</v>
       </c>
     </row>
@@ -27572,15 +27572,15 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <f>_xlfn.RANK.EQ(F5,$E5:$H5,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L5">
-        <f>_xlfn.RANK.EQ(G5,$E5:$H5,1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M5">
-        <f>_xlfn.RANK.EQ(H5,$E5:$H5,1)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -27608,15 +27608,15 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <f>_xlfn.RANK.EQ(F6,$E6:$H6,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L6">
-        <f>_xlfn.RANK.EQ(G6,$E6:$H6,1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M6">
-        <f>_xlfn.RANK.EQ(H6,$E6:$H6,1)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -27648,15 +27648,15 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <f>_xlfn.RANK.EQ(F7,$E7:$H7,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L7">
-        <f>_xlfn.RANK.EQ(G7,$E7:$H7,1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M7">
-        <f>_xlfn.RANK.EQ(H7,$E7:$H7,1)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -27684,15 +27684,15 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <f>_xlfn.RANK.EQ(F8,$E8:$H8,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L8">
-        <f>_xlfn.RANK.EQ(G8,$E8:$H8,1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M8">
-        <f>_xlfn.RANK.EQ(H8,$E8:$H8,1)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -27724,15 +27724,15 @@
         <v>2</v>
       </c>
       <c r="K9">
-        <f>_xlfn.RANK.EQ(F9,$E9:$H9,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L9">
-        <f>_xlfn.RANK.EQ(G9,$E9:$H9,1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M9">
-        <f>_xlfn.RANK.EQ(H9,$E9:$H9,1)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -27760,15 +27760,15 @@
         <v>3</v>
       </c>
       <c r="K10">
-        <f>_xlfn.RANK.EQ(F10,$E10:$H10,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L10">
-        <f>_xlfn.RANK.EQ(G10,$E10:$H10,1)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="M10">
-        <f>_xlfn.RANK.EQ(H10,$E10:$H10,1)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -27800,15 +27800,15 @@
         <v>1</v>
       </c>
       <c r="K11">
-        <f>_xlfn.RANK.EQ(F11,$E11:$H11,1)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L11">
-        <f>_xlfn.RANK.EQ(G11,$E11:$H11,1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M11">
-        <f>_xlfn.RANK.EQ(H11,$E11:$H11,1)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -27836,15 +27836,15 @@
         <v>1</v>
       </c>
       <c r="K12">
-        <f>_xlfn.RANK.EQ(F12,$E12:$H12,1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L12">
-        <f>_xlfn.RANK.EQ(G12,$E12:$H12,1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M12">
-        <f>_xlfn.RANK.EQ(H12,$E12:$H12,1)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -27876,15 +27876,15 @@
         <v>3</v>
       </c>
       <c r="K13">
-        <f>_xlfn.RANK.EQ(F13,$E13:$H13,1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L13">
-        <f>_xlfn.RANK.EQ(G13,$E13:$H13,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M13">
-        <f>_xlfn.RANK.EQ(H13,$E13:$H13,1)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -27912,15 +27912,15 @@
         <v>4</v>
       </c>
       <c r="K14">
-        <f>_xlfn.RANK.EQ(F14,$E14:$H14,1)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L14">
-        <f>_xlfn.RANK.EQ(G14,$E14:$H14,1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M14">
-        <f>_xlfn.RANK.EQ(H14,$E14:$H14,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -27952,15 +27952,15 @@
         <v>2</v>
       </c>
       <c r="K15">
-        <f>_xlfn.RANK.EQ(F15,$E15:$H15,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L15">
-        <f>_xlfn.RANK.EQ(G15,$E15:$H15,1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M15">
-        <f>_xlfn.RANK.EQ(H15,$E15:$H15,1)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -27988,15 +27988,15 @@
         <v>3</v>
       </c>
       <c r="K16">
-        <f>_xlfn.RANK.EQ(F16,$E16:$H16,1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L16">
-        <f>_xlfn.RANK.EQ(G16,$E16:$H16,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M16">
-        <f>_xlfn.RANK.EQ(H16,$E16:$H16,1)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -28028,15 +28028,15 @@
         <v>3</v>
       </c>
       <c r="K17">
-        <f>_xlfn.RANK.EQ(F17,$E17:$H17,1)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L17">
-        <f>_xlfn.RANK.EQ(G17,$E17:$H17,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M17">
-        <f>_xlfn.RANK.EQ(H17,$E17:$H17,1)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -28064,15 +28064,15 @@
         <v>2</v>
       </c>
       <c r="K18">
-        <f>_xlfn.RANK.EQ(F18,$E18:$H18,1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L18">
-        <f>_xlfn.RANK.EQ(G18,$E18:$H18,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M18">
-        <f>_xlfn.RANK.EQ(H18,$E18:$H18,1)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -28459,18 +28459,6 @@
       <c r="B30" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="J30" s="10" t="s">
         <v>94</v>
       </c>
@@ -28489,25 +28477,6 @@
         <f>1-_xlfn.CHISQ.DIST(N28,3,TRUE)</f>
         <v>0.4889978477959176</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="3">
-        <f>2*(1-_xlfn.T.DIST(J37,100,TRUE))</f>
-        <v>1</v>
-      </c>
-      <c r="F31" s="3">
-        <f>2*(1-_xlfn.T.DIST(K37,100,TRUE))</f>
-        <v>0.57739989021589366</v>
-      </c>
-      <c r="G31" s="3">
-        <f>2*(1-_xlfn.T.DIST(L37,100,TRUE))</f>
-        <v>2.7569600666045302E-2</v>
-      </c>
-      <c r="H31" s="3">
-        <f>2*(1-_xlfn.T.DIST(M37,100,TRUE))</f>
-        <v>0.3732410827341488</v>
-      </c>
       <c r="I31" s="16"/>
       <c r="K31">
         <f>ABS($J$27-$K$27)</f>
@@ -28523,25 +28492,6 @@
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="D32" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="3">
-        <f>2*(1-_xlfn.T.DIST(J38,100,TRUE))</f>
-        <v>0.57739989021589366</v>
-      </c>
-      <c r="F32" s="3">
-        <f>2*(1-_xlfn.T.DIST(K38,100,TRUE))</f>
-        <v>1</v>
-      </c>
-      <c r="G32" s="3">
-        <f>2*(1-_xlfn.T.DIST(L38,100,TRUE))</f>
-        <v>9.6655848685819556E-2</v>
-      </c>
-      <c r="H32" s="3">
-        <f>2*(1-_xlfn.T.DIST(M38,100,TRUE))</f>
-        <v>0.73801830854622086</v>
-      </c>
       <c r="I32" s="16"/>
       <c r="J32">
         <f>ABS($J$27-$K$27)</f>
@@ -28557,25 +28507,6 @@
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D33" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="3">
-        <f>2*(1-_xlfn.T.DIST(J39,100,TRUE))</f>
-        <v>2.7569600666045302E-2</v>
-      </c>
-      <c r="F33" s="3">
-        <f>2*(1-_xlfn.T.DIST(K39,100,TRUE))</f>
-        <v>9.6655848685819556E-2</v>
-      </c>
-      <c r="G33" s="3">
-        <f>2*(1-_xlfn.T.DIST(L39,100,TRUE))</f>
-        <v>1</v>
-      </c>
-      <c r="H33" s="3">
-        <f>2*(1-_xlfn.T.DIST(M39,100,TRUE))</f>
-        <v>0.18275124367193762</v>
-      </c>
       <c r="I33" s="16"/>
       <c r="J33">
         <f>ABS($J$27-$L$27)</f>
@@ -28591,25 +28522,6 @@
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D34" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="3">
-        <f>2*(1-_xlfn.T.DIST(J40,100,TRUE))</f>
-        <v>0.3732410827341488</v>
-      </c>
-      <c r="F34" s="3">
-        <f>2*(1-_xlfn.T.DIST(K40,100,TRUE))</f>
-        <v>0.73801830854622086</v>
-      </c>
-      <c r="G34" s="3">
-        <f>2*(1-_xlfn.T.DIST(L40,100,TRUE))</f>
-        <v>0.18275124367193762</v>
-      </c>
-      <c r="H34" s="3">
-        <f>2*(1-_xlfn.T.DIST(M40,100,TRUE))</f>
-        <v>1</v>
-      </c>
       <c r="I34" s="16"/>
       <c r="J34">
         <f>ABS($J$27-$M$27)</f>
@@ -28625,6 +28537,18 @@
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="E37" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K37">
         <f>K31/$O$28</f>
         <v>0.55901699437494778</v>
@@ -28634,11 +28558,30 @@
         <v>2.2360679774997902</v>
       </c>
       <c r="M37">
-        <f t="shared" ref="M37:M39" si="1">M31/$O$28</f>
+        <f t="shared" ref="M37:M39" si="4">M31/$O$28</f>
         <v>0.8944271909999163</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="3">
+        <f>2*(1-_xlfn.T.DIST(J37,100,TRUE))</f>
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <f>2*(1-_xlfn.T.DIST(K37,100,TRUE))</f>
+        <v>0.57739989021589366</v>
+      </c>
+      <c r="G38" s="3">
+        <f>2*(1-_xlfn.T.DIST(L37,100,TRUE))</f>
+        <v>2.7569600666045302E-2</v>
+      </c>
+      <c r="H38" s="3">
+        <f>2*(1-_xlfn.T.DIST(M37,100,TRUE))</f>
+        <v>0.3732410827341488</v>
+      </c>
       <c r="J38">
         <f>J32/$O$28</f>
         <v>0.55901699437494778</v>
@@ -28648,11 +28591,30 @@
         <v>1.6770509831248424</v>
       </c>
       <c r="M38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.33541019662496846</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D39" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="3">
+        <f>2*(1-_xlfn.T.DIST(J38,100,TRUE))</f>
+        <v>0.57739989021589366</v>
+      </c>
+      <c r="F39" s="3">
+        <f>2*(1-_xlfn.T.DIST(K38,100,TRUE))</f>
+        <v>1</v>
+      </c>
+      <c r="G39" s="3">
+        <f>2*(1-_xlfn.T.DIST(L38,100,TRUE))</f>
+        <v>9.6655848685819556E-2</v>
+      </c>
+      <c r="H39" s="3">
+        <f>2*(1-_xlfn.T.DIST(M38,100,TRUE))</f>
+        <v>0.73801830854622086</v>
+      </c>
       <c r="J39">
         <f>J33/$O$28</f>
         <v>2.2360679774997902</v>
@@ -28662,11 +28624,30 @@
         <v>1.6770509831248424</v>
       </c>
       <c r="M39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.3416407864998738</v>
       </c>
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D40" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="3">
+        <f>2*(1-_xlfn.T.DIST(J39,100,TRUE))</f>
+        <v>2.7569600666045302E-2</v>
+      </c>
+      <c r="F40" s="3">
+        <f>2*(1-_xlfn.T.DIST(K39,100,TRUE))</f>
+        <v>9.6655848685819556E-2</v>
+      </c>
+      <c r="G40" s="3">
+        <f>2*(1-_xlfn.T.DIST(L39,100,TRUE))</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <f>2*(1-_xlfn.T.DIST(M39,100,TRUE))</f>
+        <v>0.18275124367193762</v>
+      </c>
       <c r="J40">
         <f>J34/$O$28</f>
         <v>0.8944271909999163</v>
@@ -28680,8 +28661,29 @@
         <v>1.3416407864998738</v>
       </c>
     </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D41" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="3">
+        <f>2*(1-_xlfn.T.DIST(J40,100,TRUE))</f>
+        <v>0.3732410827341488</v>
+      </c>
+      <c r="F41" s="3">
+        <f>2*(1-_xlfn.T.DIST(K40,100,TRUE))</f>
+        <v>0.73801830854622086</v>
+      </c>
+      <c r="G41" s="3">
+        <f>2*(1-_xlfn.T.DIST(L40,100,TRUE))</f>
+        <v>0.18275124367193762</v>
+      </c>
+      <c r="H41" s="3">
+        <f>2*(1-_xlfn.T.DIST(M40,100,TRUE))</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E31:H34">
+  <conditionalFormatting sqref="E38:H41">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
